--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,234 +443,424 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DocumentReference.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>DocumentReference.masterIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Master Version Specific Identifier</t>
+  </si>
+  <si>
+    <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
+  </si>
+  <si>
+    <t>CDA Document Id extension and root.</t>
+  </si>
+  <si>
+    <t>The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>Composition.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>TXA-12</t>
+  </si>
+  <si>
+    <t>DocumentEntry.uniqueId</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier</t>
+  </si>
+  <si>
+    <t>Other identifiers for the document</t>
+  </si>
+  <si>
+    <t>Other identifiers associated with the document, including version independent identifiers.</t>
+  </si>
+  <si>
+    <t>.id / .setId</t>
+  </si>
+  <si>
+    <t>TXA-16?</t>
+  </si>
+  <si>
+    <t>DocumentEntry.entryUUID</t>
+  </si>
+  <si>
+    <t>DocumentReference.status</t>
+  </si>
+  <si>
+    <t>current | superseded | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of this document reference.</t>
+  </si>
+  <si>
+    <t>This is the status of the DocumentReference object, which might be independent from the docStatus element.
+This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of the document reference.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-reference-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>interim: .completionCode="IN" &amp; ./statusCode[isNormalDatatype()]="active";  final: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and not(./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseDocument", code) and isNormalAct()]);  amended: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and ./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseDocument", code) and isNormalAct() and statusCode="completed"];  withdrawn : .completionCode=NI &amp;&amp;  ./statusCode[isNormalDatatype()]="obsolete"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>TXA-19</t>
+  </si>
+  <si>
+    <t>DocumentEntry.availabilityStatus</t>
+  </si>
+  <si>
+    <t>DocumentReference.docStatus</t>
+  </si>
+  <si>
+    <t>preliminary | final | amended | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of the underlying document.</t>
+  </si>
+  <si>
+    <t>The document that is pointed to might be in various lifecycle states.</t>
+  </si>
+  <si>
+    <t>Status of the underlying document.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/composition-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Composition.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>TXA-17</t>
+  </si>
+  <si>
+    <t>DocumentReference.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Kind of document (LOINC if possible)</t>
+  </si>
+  <si>
+    <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
+  </si>
+  <si>
+    <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
+  </si>
+  <si>
+    <t>Precise type of clinical document.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>Composition.type</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/code/@code 
+The typeCode should be mapped from the ClinicalDocument/code element to a set of document type codes configured in the affinity domain. One suggested coding system to use for typeCode is LOINC, in which case the mapping step can be omitted.</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>TXA-2</t>
+  </si>
+  <si>
+    <t>DocumentEntry.type</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DocumentReference.extension:typeDocument</t>
-  </si>
-  <si>
-    <t>typeDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop-sante.fr/fhir/StructureDefinition/DocumentTypeFr}
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Extension pour indiquer le type de document dans DocumentReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/PreadmissionValueSetDocumentTypeFr</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-code-system</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>DocumentReference.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>DocumentReference.masterIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Master Version Specific Identifier</t>
-  </si>
-  <si>
-    <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
-  </si>
-  <si>
-    <t>CDA Document Id extension and root.</t>
-  </si>
-  <si>
-    <t>The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>Composition.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>TXA-12</t>
-  </si>
-  <si>
-    <t>DocumentEntry.uniqueId</t>
-  </si>
-  <si>
-    <t>DocumentReference.identifier</t>
-  </si>
-  <si>
-    <t>Other identifiers for the document</t>
-  </si>
-  <si>
-    <t>Other identifiers associated with the document, including version independent identifiers.</t>
-  </si>
-  <si>
-    <t>.id / .setId</t>
-  </si>
-  <si>
-    <t>TXA-16?</t>
-  </si>
-  <si>
-    <t>DocumentEntry.entryUUID</t>
-  </si>
-  <si>
-    <t>DocumentReference.status</t>
-  </si>
-  <si>
-    <t>current | superseded | entered-in-error</t>
-  </si>
-  <si>
-    <t>The status of this document reference.</t>
-  </si>
-  <si>
-    <t>This is the status of the DocumentReference object, which might be independent from the docStatus element.
-This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The status of the document reference.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-reference-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>interim: .completionCode="IN" &amp; ./statusCode[isNormalDatatype()]="active";  final: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and not(./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseDocument", code) and isNormalAct()]);  amended: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and ./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseDocument", code) and isNormalAct() and statusCode="completed"];  withdrawn : .completionCode=NI &amp;&amp;  ./statusCode[isNormalDatatype()]="obsolete"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>TXA-19</t>
-  </si>
-  <si>
-    <t>DocumentEntry.availabilityStatus</t>
-  </si>
-  <si>
-    <t>DocumentReference.docStatus</t>
-  </si>
-  <si>
-    <t>preliminary | final | amended | entered-in-error</t>
-  </si>
-  <si>
-    <t>The status of the underlying document.</t>
-  </si>
-  <si>
-    <t>The document that is pointed to might be in various lifecycle states.</t>
-  </si>
-  <si>
-    <t>Status of the underlying document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/composition-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Composition.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>TXA-17</t>
-  </si>
-  <si>
-    <t>DocumentReference.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Kind of document (LOINC if possible)</t>
-  </si>
-  <si>
-    <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
-  </si>
-  <si>
-    <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
-  </si>
-  <si>
-    <t>Precise type of clinical document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>Composition.type</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/code/@code 
-The typeCode should be mapped from the ClinicalDocument/code element to a set of document type codes configured in the affinity domain. One suggested coding system to use for typeCode is LOINC, in which case the mapping step can be omitted.</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>TXA-2</t>
-  </si>
-  <si>
-    <t>DocumentEntry.type</t>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -894,32 +1084,7 @@
     <t>DocumentReference.relatesTo.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DocumentReference.relatesTo.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1109,9 +1274,6 @@
     <t>DocumentReference.content.attachment.extension</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
@@ -1309,10 +1471,6 @@
   </si>
   <si>
     <t>DocumentReference.content.format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Format/content rules for the document</t>
@@ -1846,12 +2004,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ57"/>
+  <dimension ref="A1:AQ67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.55078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1874,7 +2032,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.66796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.8671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2892,11 +3050,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>83</v>
@@ -2911,15 +3069,17 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>81</v>
@@ -2956,14 +3116,16 @@
         <v>81</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>144</v>
@@ -2987,7 +3149,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -3007,41 +3169,43 @@
         <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
       </c>
@@ -3089,7 +3253,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>82</v>
@@ -3098,7 +3262,7 @@
         <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>145</v>
@@ -3110,7 +3274,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3134,26 +3298,26 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>153</v>
@@ -3214,48 +3378,48 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AL11" t="s" s="2">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3266,7 +3430,7 @@
         <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3278,20 +3442,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3339,13 +3499,13 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>81</v>
@@ -3354,33 +3514,33 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AO12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AP12" t="s" s="2">
+      <c r="AQ12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3388,30 +3548,32 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -3436,13 +3598,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3460,13 +3622,13 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
@@ -3475,33 +3637,33 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3509,7 +3671,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>94</v>
@@ -3518,7 +3680,7 @@
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>95</v>
@@ -3527,13 +3689,13 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3559,34 +3721,34 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>94</v>
@@ -3598,33 +3760,33 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>81</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>188</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3632,7 +3794,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>94</v>
@@ -3647,16 +3809,16 @@
         <v>95</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3682,13 +3844,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3706,7 +3868,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3721,33 +3883,33 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3767,20 +3929,18 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3805,13 +3965,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3829,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -3841,40 +4001,40 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3890,19 +4050,19 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3928,31 +4088,31 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -3964,36 +4124,36 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4001,7 +4161,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
@@ -4016,16 +4176,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4049,13 +4213,11 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4079,7 +4241,7 @@
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4088,37 +4250,37 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4134,20 +4296,18 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4196,7 +4356,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4208,22 +4368,22 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>81</v>
@@ -4234,14 +4394,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4257,19 +4417,19 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4307,19 +4467,19 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4331,36 +4491,36 @@
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4380,21 +4540,23 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>257</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4403,7 +4565,7 @@
         <v>81</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>81</v>
@@ -4442,7 +4604,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4457,33 +4619,33 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4503,19 +4665,19 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>268</v>
+        <v>206</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4565,7 +4727,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4580,13 +4742,13 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4595,7 +4757,7 @@
         <v>81</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -4603,10 +4765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4617,7 +4779,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4629,18 +4791,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>275</v>
+        <v>114</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4688,13 +4850,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4706,10 +4868,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4718,18 +4880,18 @@
         <v>81</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4749,19 +4911,21 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4809,7 +4973,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4821,7 +4985,7 @@
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4830,7 +4994,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4839,7 +5003,7 @@
         <v>81</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>81</v>
@@ -4847,21 +5011,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4870,21 +5034,23 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4932,19 +5098,19 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -4953,7 +5119,7 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4962,7 +5128,7 @@
         <v>81</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -4970,45 +5136,45 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>156</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5057,19 +5223,19 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5078,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>137</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5087,7 +5253,7 @@
         <v>81</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>81</v>
@@ -5095,21 +5261,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5121,16 +5287,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5156,13 +5322,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5180,13 +5346,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5198,30 +5364,30 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5229,7 +5395,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>94</v>
@@ -5244,13 +5410,13 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5301,10 +5467,10 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>94</v>
@@ -5316,37 +5482,37 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5365,20 +5531,18 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5426,7 +5590,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5441,33 +5605,33 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5490,20 +5654,18 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5527,13 +5689,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5551,7 +5713,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5566,33 +5728,33 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5600,11 +5762,11 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5612,18 +5774,20 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5672,13 +5836,13 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH31" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
@@ -5687,33 +5851,33 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5736,15 +5900,17 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5793,7 +5959,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5805,16 +5971,16 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5831,14 +5997,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5854,19 +6020,19 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>338</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>155</v>
+        <v>341</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5916,7 +6082,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5928,16 +6094,16 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5949,51 +6115,47 @@
         <v>81</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>207</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6041,19 +6203,19 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6224,7 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6079,21 +6241,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6102,18 +6264,20 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>343</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>141</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6162,80 +6326,84 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>216</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6283,19 +6451,19 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6304,7 +6472,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>287</v>
+        <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6321,21 +6489,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6344,19 +6512,19 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6382,52 +6550,52 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AG37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>81</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>287</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6439,15 +6607,15 @@
         <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6470,18 +6638,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>114</v>
+        <v>362</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>356</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6493,7 +6659,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6505,13 +6671,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6529,10 +6695,10 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>94</v>
@@ -6547,10 +6713,10 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6559,18 +6725,18 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6593,17 +6759,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6616,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -6628,13 +6796,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6673,7 +6841,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6682,18 +6850,18 @@
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6704,7 +6872,7 @@
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6713,22 +6881,22 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>371</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6753,13 +6921,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6783,7 +6951,7 @@
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
@@ -6795,30 +6963,30 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>384</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6826,10 +6994,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6841,20 +7009,16 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6866,7 +7030,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>385</v>
+        <v>81</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -6902,13 +7066,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6920,10 +7084,10 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6932,7 +7096,7 @@
         <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -6940,10 +7104,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6963,23 +7127,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>390</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>391</v>
+        <v>207</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7027,7 +7187,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7039,7 +7199,7 @@
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -7048,7 +7208,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>210</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7065,21 +7225,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7088,23 +7248,21 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>212</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7152,19 +7310,19 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>402</v>
+        <v>216</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -7173,7 +7331,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>210</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7190,43 +7348,45 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>407</v>
+        <v>149</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7239,7 +7399,7 @@
         <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>81</v>
@@ -7275,19 +7435,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7296,7 +7456,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7313,10 +7473,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7324,7 +7484,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>94</v>
@@ -7339,18 +7499,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7398,10 +7556,10 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>94</v>
@@ -7416,30 +7574,30 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7459,20 +7617,18 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>418</v>
+        <v>206</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>419</v>
+        <v>207</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7497,13 +7653,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7521,7 +7677,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>209</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7533,19 +7689,19 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>338</v>
+        <v>210</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7554,26 +7710,26 @@
         <v>81</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7582,19 +7738,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
+        <v>212</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>430</v>
+        <v>143</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7632,31 +7788,31 @@
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>216</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7665,7 +7821,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>431</v>
+        <v>210</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7682,10 +7838,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7693,7 +7849,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -7705,19 +7861,21 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>284</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>285</v>
+        <v>409</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7729,7 +7887,7 @@
         <v>81</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>81</v>
@@ -7741,13 +7899,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7765,7 +7923,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>286</v>
+        <v>414</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7777,7 +7935,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7786,7 +7944,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7795,7 +7953,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -7803,21 +7961,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7826,21 +7984,21 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7852,7 +8010,7 @@
         <v>81</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>81</v>
@@ -7864,13 +8022,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7888,19 +8046,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>291</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7909,7 +8067,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>287</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7926,45 +8084,45 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>139</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>294</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>295</v>
+        <v>427</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>155</v>
+        <v>428</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>156</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8013,19 +8171,19 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -8034,7 +8192,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>137</v>
+        <v>431</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8043,7 +8201,7 @@
         <v>81</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8051,10 +8209,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8062,7 +8220,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>94</v>
@@ -8074,19 +8232,23 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8098,7 +8260,7 @@
         <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>81</v>
@@ -8134,13 +8296,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -8149,10 +8311,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>441</v>
@@ -8161,10 +8323,10 @@
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8186,7 +8348,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8195,21 +8357,23 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>199</v>
+        <v>444</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8233,13 +8397,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8257,13 +8421,13 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
@@ -8275,7 +8439,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>450</v>
@@ -8290,15 +8454,15 @@
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8321,16 +8485,20 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8378,7 +8546,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8396,13 +8564,13 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>457</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>458</v>
+        <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8411,15 +8579,15 @@
         <v>81</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8439,19 +8607,21 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8463,7 +8633,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8475,31 +8645,31 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8517,13 +8687,13 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8532,15 +8702,15 @@
         <v>81</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8560,22 +8730,20 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>199</v>
+        <v>466</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8600,13 +8768,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8624,7 +8792,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8642,13 +8810,13 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8657,15 +8825,15 @@
         <v>81</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8685,18 +8853,20 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>478</v>
+        <v>218</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8721,13 +8891,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8745,7 +8915,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -8763,13 +8933,13 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>229</v>
+        <v>477</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>230</v>
+        <v>393</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8778,15 +8948,15 @@
         <v>81</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8797,7 +8967,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8806,19 +8976,19 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8868,13 +9038,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -8886,22 +9056,1246 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="B60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="B61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
+      <c r="L61" t="s" s="2">
         <v>490</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -706,7 +706,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/PreadmissionValueSetDocumentTypeFr</t>
+    <t>PreadmissionDocumentTypeFrValueSet</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -716,127 +716,6 @@
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-code-system</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>DocumentReference.type.text</t>
@@ -2004,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ67"/>
+  <dimension ref="A1:AQ60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
@@ -2032,7 +1911,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.66796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.8671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4296,19 +4175,23 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4356,7 +4239,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4368,7 +4251,7 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4377,7 +4260,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4386,7 +4269,7 @@
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4394,14 +4277,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4417,19 +4300,19 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4455,31 +4338,31 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4491,36 +4374,36 @@
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4543,20 +4426,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4565,7 +4444,7 @@
         <v>81</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>81</v>
@@ -4604,7 +4483,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4619,37 +4498,37 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4668,16 +4547,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4727,7 +4606,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4742,22 +4621,22 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>81</v>
@@ -4765,10 +4644,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4779,7 +4658,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4791,18 +4670,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4850,13 +4729,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4865,33 +4744,33 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4911,21 +4790,21 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4973,7 +4852,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4988,33 +4867,33 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5034,23 +4913,21 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -5098,7 +4975,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5113,13 +4990,13 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5128,7 +5005,7 @@
         <v>81</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>81</v>
@@ -5136,10 +5013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5150,7 +5027,7 @@
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5162,20 +5039,18 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5223,13 +5098,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -5241,10 +5116,10 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5253,29 +5128,29 @@
         <v>81</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5284,20 +5159,18 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5322,13 +5195,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5346,59 +5219,59 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5407,18 +5280,20 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>141</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5467,82 +5342,84 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>216</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>210</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5590,34 +5467,34 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>81</v>
@@ -5628,10 +5505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5639,10 +5516,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5654,16 +5531,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5689,13 +5566,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5713,13 +5590,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5728,33 +5605,33 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5762,7 +5639,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>94</v>
@@ -5774,20 +5651,18 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5836,10 +5711,10 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>94</v>
@@ -5851,33 +5726,33 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5897,21 +5772,23 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5959,7 +5836,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5974,33 +5851,33 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6023,18 +5900,20 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6058,13 +5937,13 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -6082,7 +5961,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6100,30 +5979,30 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6131,10 +6010,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6143,16 +6022,16 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>207</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>208</v>
+        <v>351</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6203,28 +6082,28 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>81</v>
+        <v>352</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6241,21 +6120,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6267,17 +6146,15 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6326,19 +6203,19 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6364,14 +6241,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>348</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6384,26 +6261,24 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>212</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O36" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6451,7 +6326,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6472,7 +6347,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6489,44 +6364,46 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6550,13 +6427,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>356</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6574,28 +6451,28 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6607,15 +6484,15 @@
         <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6638,13 +6515,13 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6695,7 +6572,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -6713,30 +6590,30 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6756,23 +6633,19 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>369</v>
+        <v>207</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6820,7 +6693,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>209</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6832,7 +6705,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6841,7 +6714,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>373</v>
+        <v>210</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6850,22 +6723,22 @@
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6881,23 +6754,21 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>212</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6921,31 +6792,31 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>216</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6957,36 +6828,36 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>210</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6997,7 +6868,7 @@
         <v>94</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -7009,16 +6880,18 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7030,7 +6903,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7042,13 +6915,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>372</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -7066,13 +6939,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -7084,10 +6957,10 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -7096,7 +6969,7 @@
         <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -7104,10 +6977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7127,19 +7000,21 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>207</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>208</v>
+        <v>379</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7151,7 +7026,7 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>81</v>
@@ -7163,13 +7038,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7187,7 +7062,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>209</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7199,7 +7074,7 @@
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -7208,7 +7083,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>210</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7225,21 +7100,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7251,18 +7126,20 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>140</v>
+        <v>385</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>141</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>212</v>
+        <v>387</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7310,19 +7187,19 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -7331,7 +7208,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>210</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7340,7 +7217,7 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7348,45 +7225,45 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>140</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>396</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>143</v>
+        <v>397</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>149</v>
+        <v>398</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7399,7 +7276,7 @@
         <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>81</v>
@@ -7435,19 +7312,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7456,7 +7333,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>137</v>
+        <v>401</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7465,7 +7342,7 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7473,10 +7350,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7484,7 +7361,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>94</v>
@@ -7499,16 +7376,20 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7556,10 +7437,10 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>94</v>
@@ -7574,30 +7455,30 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7617,19 +7498,23 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>206</v>
+        <v>385</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>207</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7677,7 +7562,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>209</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7689,7 +7574,7 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7698,7 +7583,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>210</v>
+        <v>417</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7715,21 +7600,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7738,21 +7623,21 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7764,7 +7649,7 @@
         <v>81</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>81</v>
@@ -7788,31 +7673,31 @@
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>216</v>
+        <v>423</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7821,7 +7706,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>210</v>
+        <v>424</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7838,10 +7723,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7849,7 +7734,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -7864,17 +7749,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>114</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7887,7 +7772,7 @@
         <v>81</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>81</v>
@@ -7899,13 +7784,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7923,7 +7808,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7944,7 +7829,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7953,7 +7838,7 @@
         <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -7961,10 +7846,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7987,18 +7872,18 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -8010,7 +7895,7 @@
         <v>81</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>81</v>
@@ -8025,10 +7910,10 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>119</v>
+        <v>435</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>120</v>
+        <v>436</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8046,7 +7931,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8064,13 +7949,13 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8079,15 +7964,15 @@
         <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8107,23 +7992,21 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>298</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8171,7 +8054,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8192,7 +8075,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8201,7 +8084,7 @@
         <v>81</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8209,10 +8092,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8232,23 +8115,19 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>434</v>
+        <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>435</v>
+        <v>207</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8260,7 +8139,7 @@
         <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>81</v>
@@ -8296,7 +8175,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8308,7 +8187,7 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -8317,7 +8196,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>441</v>
+        <v>210</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8326,7 +8205,7 @@
         <v>81</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8334,21 +8213,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8357,23 +8236,21 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>444</v>
+        <v>140</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>141</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
+        <v>212</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8421,19 +8298,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>216</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8442,7 +8319,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8459,45 +8336,45 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>425</v>
+        <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>452</v>
+        <v>309</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>453</v>
+        <v>310</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>454</v>
+        <v>143</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>455</v>
+        <v>149</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8546,19 +8423,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>311</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8567,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8584,10 +8461,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8595,7 +8472,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>94</v>
@@ -8607,21 +8484,19 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>206</v>
+        <v>449</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8633,7 +8508,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8669,13 +8544,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8684,19 +8559,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
@@ -8707,10 +8582,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8721,7 +8596,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8730,21 +8605,21 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>466</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8768,13 +8643,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8792,13 +8667,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8810,10 +8685,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8825,15 +8700,15 @@
         <v>81</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8856,17 +8731,15 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8891,13 +8764,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8915,7 +8788,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -8933,13 +8806,13 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>393</v>
+        <v>470</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8948,15 +8821,15 @@
         <v>81</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8976,20 +8849,18 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>338</v>
+        <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9014,13 +8885,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -9038,7 +8909,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9056,13 +8927,13 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -9071,15 +8942,15 @@
         <v>81</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9102,16 +8973,20 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>207</v>
+        <v>483</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -9135,13 +9010,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -9159,7 +9034,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>209</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9171,19 +9046,19 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>210</v>
+        <v>479</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9192,26 +9067,26 @@
         <v>81</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -9223,17 +9098,15 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>141</v>
+        <v>492</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9282,31 +9155,31 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>216</v>
+        <v>490</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9315,19 +9188,19 @@
         <v>81</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9340,26 +9213,24 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>496</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>349</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>350</v>
+        <v>498</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9407,7 +9278,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>351</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9419,19 +9290,19 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>137</v>
+        <v>501</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9440,862 +9311,7 @@
         <v>81</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AM62" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-documentreference-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-documentreference-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-documentreference-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-documentreference-fr</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FHIR pour un document administratif de préadmission</t>
+    <t>Profil DocumentReference pour un document administratif de préadmission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -621,10 +621,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>Precise type of clinical document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-document-type-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -649,7 +646,225 @@
     <t>DocumentEntry.type</t>
   </si>
   <si>
-    <t>DocumentReference.type.id</t>
+    <t>DocumentReference.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claxs
+</t>
+  </si>
+  <si>
+    <t>Categorization of document</t>
+  </si>
+  <si>
+    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
+  </si>
+  <si>
+    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>High-level kind of a clinical document at a macro level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+  </si>
+  <si>
+    <t>Composition.class</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
+  </si>
+  <si>
+    <t>DocumentEntry.class</t>
+  </si>
+  <si>
+    <t>DocumentReference.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+</t>
+  </si>
+  <si>
+    <t>Who/what is the subject of the document</t>
+  </si>
+  <si>
+    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Composition.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/recordTarget/</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>PID-3 (No standard way to define a Practitioner or Group subject in HL7 v2 MDM message)</t>
+  </si>
+  <si>
+    <t>DocumentEntry.patientId</t>
+  </si>
+  <si>
+    <t>DocumentReference.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indexed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When this document reference was created</t>
+  </si>
+  <si>
+    <t>When the document reference was created.</t>
+  </si>
+  <si>
+    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>Composition.date</t>
+  </si>
+  <si>
+    <t>.availabilityTime[type="TS"]</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>DocumentReference.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who and/or what authored the document</t>
+  </si>
+  <si>
+    <t>Identifies who is responsible for adding the information to the document.</t>
+  </si>
+  <si>
+    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>Composition.author</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUT"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/author</t>
+  </si>
+  <si>
+    <t>TXA-9 (No standard way to indicate a Device in HL7 v2 MDM message)</t>
+  </si>
+  <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
+    <t>DocumentReference.authenticator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+</t>
+  </si>
+  <si>
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+  </si>
+  <si>
+    <t>Composition.attester</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/legalAuthenticator</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>TXA-10</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>DocumentReference.custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+  </si>
+  <si>
+    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
+  </si>
+  <si>
+    <t>Composition.custodian</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Relationships to other documents</t>
+  </si>
+  <si>
+    <t>Relationships that this document has with other document references that already exist.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo</t>
+  </si>
+  <si>
+    <t>.outboundRelationship</t>
+  </si>
+  <si>
+    <t>DocumentEntry Associations</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -668,302 +883,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DocumentReference.type.extension</t>
+    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>PreadmissionDocumentTypeFrValueSet</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>DocumentReference.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claxs
-</t>
-  </si>
-  <si>
-    <t>Categorization of document</t>
-  </si>
-  <si>
-    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
-  </si>
-  <si>
-    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
-  </si>
-  <si>
-    <t>Composition.class</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
-  </si>
-  <si>
-    <t>DocumentEntry.class</t>
-  </si>
-  <si>
-    <t>DocumentReference.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
-</t>
-  </si>
-  <si>
-    <t>Who/what is the subject of the document</t>
-  </si>
-  <si>
-    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>Composition.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/recordTarget/</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>PID-3 (No standard way to define a Practitioner or Group subject in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.patientId</t>
-  </si>
-  <si>
-    <t>DocumentReference.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indexed
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When this document reference was created</t>
-  </si>
-  <si>
-    <t>When the document reference was created.</t>
-  </si>
-  <si>
-    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>Composition.date</t>
-  </si>
-  <si>
-    <t>.availabilityTime[type="TS"]</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>DocumentReference.author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who and/or what authored the document</t>
-  </si>
-  <si>
-    <t>Identifies who is responsible for adding the information to the document.</t>
-  </si>
-  <si>
-    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>Composition.author</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUT"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/author</t>
-  </si>
-  <si>
-    <t>TXA-9 (No standard way to indicate a Device in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.author</t>
-  </si>
-  <si>
-    <t>DocumentReference.authenticator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
-</t>
-  </si>
-  <si>
-    <t>Who/what authenticated the document</t>
-  </si>
-  <si>
-    <t>Which person or organization authenticates that this document is valid.</t>
-  </si>
-  <si>
-    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
-  </si>
-  <si>
-    <t>Composition.attester</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/legalAuthenticator</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>TXA-10</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>DocumentReference.custodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
-  </si>
-  <si>
-    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
-  </si>
-  <si>
-    <t>Composition.custodian</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
-  </si>
-  <si>
-    <t>Composition.relatesTo</t>
-  </si>
-  <si>
-    <t>.outboundRelationship</t>
-  </si>
-  <si>
-    <t>DocumentEntry Associations</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1153,6 +1079,16 @@
     <t>DocumentReference.content.attachment.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
@@ -1350,6 +1286,10 @@
   </si>
   <si>
     <t>DocumentReference.content.format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Format/content rules for the document</t>
@@ -1883,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ60"/>
+  <dimension ref="A1:AQ56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
@@ -1911,7 +1851,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.66796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.8671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3723,13 +3663,11 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y15" s="2"/>
+      <c r="Z15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3762,44 +3700,44 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AP15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3808,18 +3746,20 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3844,13 +3784,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3868,59 +3808,59 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3929,20 +3869,18 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3979,16 +3917,16 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>216</v>
@@ -3997,50 +3935,50 @@
         <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
@@ -4055,20 +3993,18 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4092,11 +4028,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4114,13 +4052,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4129,22 +4067,22 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4152,10 +4090,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4166,7 +4104,7 @@
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4178,20 +4116,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4239,13 +4175,13 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
@@ -4254,44 +4190,44 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4300,19 +4236,19 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4338,13 +4274,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4362,13 +4298,13 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
@@ -4377,33 +4313,33 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4423,18 +4359,20 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4483,7 +4421,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4498,44 +4436,44 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4547,16 +4485,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4606,13 +4544,13 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
@@ -4621,33 +4559,33 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4658,7 +4596,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4667,20 +4605,18 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4729,59 +4665,59 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4793,16 +4729,16 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="N24" t="s" s="2">
-        <v>283</v>
+        <v>143</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4852,82 +4788,84 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AN24" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4975,28 +4913,28 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5013,10 +4951,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5024,10 +4962,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5039,16 +4977,16 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>298</v>
+        <v>114</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5074,13 +5012,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5098,13 +5036,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -5116,10 +5054,10 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5131,15 +5069,15 @@
         <v>81</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5147,7 +5085,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>94</v>
@@ -5159,16 +5097,16 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5219,10 +5157,10 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>94</v>
@@ -5231,16 +5169,16 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -5252,26 +5190,26 @@
         <v>81</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>81</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5280,21 +5218,23 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5342,19 +5282,19 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5363,7 +5303,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>210</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5372,22 +5312,22 @@
         <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5400,25 +5340,25 @@
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>143</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>149</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5443,13 +5383,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5467,7 +5407,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5479,36 +5419,36 @@
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5519,7 +5459,7 @@
         <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5531,17 +5471,15 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>114</v>
+        <v>267</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5566,13 +5504,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5590,13 +5528,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5608,10 +5546,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5623,15 +5561,15 @@
         <v>81</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5639,7 +5577,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>94</v>
@@ -5651,16 +5589,16 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>323</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5711,10 +5649,10 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>94</v>
@@ -5723,16 +5661,16 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>326</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5744,26 +5682,26 @@
         <v>81</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5772,23 +5710,21 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>141</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5836,19 +5772,19 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5857,7 +5793,7 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5866,22 +5802,22 @@
         <v>81</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5894,25 +5830,25 @@
         <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>339</v>
+        <v>143</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>340</v>
+        <v>149</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5937,13 +5873,13 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -5961,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5973,36 +5909,36 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6013,7 +5949,7 @@
         <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -6025,13 +5961,13 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6082,13 +6018,13 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
@@ -6100,30 +6036,30 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6146,13 +6082,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6203,7 +6139,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6224,7 +6160,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6241,10 +6177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6273,7 +6209,7 @@
         <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>143</v>
@@ -6314,19 +6250,19 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>81</v>
+        <v>345</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6347,7 +6283,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6364,45 +6300,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>149</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6415,7 +6349,7 @@
         <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>81</v>
@@ -6427,13 +6361,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6451,19 +6385,19 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6472,7 +6406,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>137</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6481,7 +6415,7 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6489,10 +6423,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6500,7 +6434,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>94</v>
@@ -6515,16 +6449,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6536,7 +6472,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6548,13 +6484,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6572,10 +6508,10 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>94</v>
@@ -6590,30 +6526,30 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6636,16 +6572,20 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>207</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6693,7 +6633,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6705,7 +6645,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6714,7 +6654,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6723,7 +6663,7 @@
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>81</v>
+        <v>371</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6731,21 +6671,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6754,21 +6694,23 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>373</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>141</v>
+        <v>374</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>375</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6780,7 +6722,7 @@
         <v>81</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>81</v>
@@ -6804,31 +6746,31 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6837,7 +6779,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6846,7 +6788,7 @@
         <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>81</v>
@@ -6854,10 +6796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6865,7 +6807,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>94</v>
@@ -6880,17 +6822,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6903,7 +6847,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -6915,13 +6859,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6939,7 +6883,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -6960,7 +6904,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6969,7 +6913,7 @@
         <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -6977,10 +6921,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7003,17 +6947,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>364</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7026,7 +6972,7 @@
         <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>81</v>
@@ -7038,13 +6984,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7062,7 +7008,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7083,7 +7029,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7100,10 +7046,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7123,22 +7069,20 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>275</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7151,7 +7095,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7187,7 +7131,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7208,7 +7152,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7217,7 +7161,7 @@
         <v>81</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7225,10 +7169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7251,19 +7195,17 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7276,7 +7218,7 @@
         <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>81</v>
@@ -7312,7 +7254,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7333,7 +7275,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7342,7 +7284,7 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7350,10 +7292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7376,20 +7318,18 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7413,13 +7353,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7437,7 +7377,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7455,13 +7395,13 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>410</v>
+        <v>329</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7470,15 +7410,15 @@
         <v>81</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7501,20 +7441,18 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>385</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7562,7 +7500,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7583,7 +7521,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7600,10 +7538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7623,21 +7561,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>419</v>
+        <v>276</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>420</v>
+        <v>277</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7649,7 +7585,7 @@
         <v>81</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>81</v>
@@ -7685,7 +7621,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>423</v>
+        <v>278</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7697,7 +7633,7 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7706,7 +7642,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>424</v>
+        <v>279</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7723,21 +7659,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7746,21 +7682,21 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>426</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7808,19 +7744,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>430</v>
+        <v>282</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7829,7 +7765,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>410</v>
+        <v>279</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7846,44 +7782,46 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>432</v>
+        <v>285</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
+        <v>286</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7907,13 +7845,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7931,31 +7869,31 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>431</v>
+        <v>287</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>353</v>
+        <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7964,15 +7902,15 @@
         <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7980,7 +7918,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>94</v>
@@ -7992,20 +7930,18 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>298</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8054,13 +7990,13 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
@@ -8069,19 +8005,19 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>81</v>
@@ -8092,10 +8028,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8106,7 +8042,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8118,15 +8054,17 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>207</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8151,13 +8089,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8175,28 +8113,28 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>209</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>210</v>
+        <v>443</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8208,26 +8146,26 @@
         <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8236,20 +8174,18 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>140</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>141</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8298,31 +8234,31 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>216</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>210</v>
+        <v>450</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8331,51 +8267,47 @@
         <v>81</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>81</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>309</v>
+        <v>454</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8399,13 +8331,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8423,31 +8355,31 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>311</v>
+        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>137</v>
+        <v>459</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8456,15 +8388,15 @@
         <v>81</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8472,7 +8404,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>94</v>
@@ -8487,16 +8419,20 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>449</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8520,13 +8456,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8544,13 +8480,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8559,33 +8495,33 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8596,7 +8532,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8608,17 +8544,15 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>471</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8643,13 +8577,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8667,13 +8601,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8685,13 +8619,13 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>462</v>
+        <v>221</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>463</v>
+        <v>222</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8700,15 +8634,15 @@
         <v>81</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8719,7 +8653,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8728,18 +8662,20 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8788,13 +8724,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8806,13 +8742,13 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8821,497 +8757,7 @@
         <v>81</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L58" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1343,7 +1343,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-encounter-fr)
 </t>
   </si>
   <si>
@@ -1836,7 +1836,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.81640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.01171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-documentreference-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
